--- a/04_output/P04/M04_Audit_B099.xlsx
+++ b/04_output/P04/M04_Audit_B099.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_B099" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Audit_B099'!$A$1:$H$5</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="Rp #,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +31,8 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,7 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00123B5D"/>
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF4F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,14 +60,14 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00D7DEE8"/>
+        <color rgb="00D9E1F2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -78,8 +78,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,22 +442,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="16.7" customWidth="1" min="1" max="1"/>
+    <col width="13.55" customWidth="1" min="2" max="2"/>
+    <col width="12.5" customWidth="1" min="3" max="3"/>
+    <col width="13.55" customWidth="1" min="4" max="4"/>
+    <col width="13.55" customWidth="1" min="5" max="5"/>
+    <col width="13.55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Transaction_ID</t>
@@ -487,16 +484,6 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Profit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Branch_ID</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Audit</t>
         </is>
       </c>
     </row>
@@ -527,16 +514,6 @@
       <c r="F2" s="3" t="n">
         <v>29947.71</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>B099</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Orphan - tidak ada di Dim_Branch</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -565,16 +542,6 @@
       <c r="F3" s="3" t="n">
         <v>6939.71</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>B099</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Orphan - tidak ada di Dim_Branch</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -603,16 +570,6 @@
       <c r="F4" s="3" t="n">
         <v>46788.45</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>B099</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Orphan - tidak ada di Dim_Branch</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -641,36 +598,70 @@
       <c r="F5" s="3" t="n">
         <v>55885.06</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>B099</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Orphan - tidak ada di Dim_Branch</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E6" s="5">
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3">
         <f>SUM(E2:E5)</f>
         <v/>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <f>SUM(F2:F5)</f>
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Keputusan</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Unknown / Unmapped Branch</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alasan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Transaksi memiliki atribut transaksi yang cukup, tetapi tidak ada bukti untuk memetakan B099 ke cabang resmi. Pertahankan total perusahaan tanpa membuat atribusi cabang palsu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jumlah 4 transaksi; benchmark Revenue ~Rp362.760,93 dan Profit ~Rp139.560,93.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H5"/>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B8:F8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>